--- a/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
+++ b/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="encore-qa-tracker" state="visible" r:id="rId4"/>
   </sheets>
@@ -14,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="171">
   <si>
     <t>COLOR KEY - our verification finding per item (rows sorted RED &gt; YELLOW &gt; GREEN within each Type section)</t>
   </si>
@@ -136,6 +133,33 @@
     <t>Delete should remain available so the row can be removed.</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Product bug</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Pricing Detail (Max Discount column)</t>
+  </si>
+  <si>
+    <t>On the Pricing Detail tab of a price book, click into a Max Discount cell, type a value over 100 (e.g. 333), then try to click or tab out of the cell.</t>
+  </si>
+  <si>
+    <t>The field will not let you leave it — clicking elsewhere or pressing Tab does nothing and the cursor stays trapped in the cell. No error message, tooltip, or validation hint is shown. The only way out is to manually lower the value to 100 or less.</t>
+  </si>
+  <si>
+    <t>An out-of-range entry should show a clear validation message AND still let the user move out of the field — it should not silently trap the cursor with no feedback.</t>
+  </si>
+  <si>
+    <t>Out-of-range input appears to block the field’s blur/commit without surfacing a validation error.</t>
+  </si>
+  <si>
+    <t>Action required. Confirmed live by manual entry on the current site (2026-06-09). The 100% cap itself is reasonable; the defect is the silent focus-trap with no error and no way out.</t>
+  </si>
+  <si>
     <t>A1</t>
   </si>
   <si>
@@ -373,6 +397,51 @@
     <t>Should already-added locations be hidden from the dialog?</t>
   </si>
   <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Pricing Detail (grid)</t>
+  </si>
+  <si>
+    <t>On the Pricing Detail tab of an existing price book, look for a way to expand a product-group row to see the items inside it.</t>
+  </si>
+  <si>
+    <t>The grid is flat — each product group is a single, non-expandable row with no way to drill into items. The written spec describes expanding a product group to show the items inside it.</t>
+  </si>
+  <si>
+    <t>Is the flat grid interim (the expandable group→items view still planned), or is the flat list the final design? Our coverage currently asserts the flat grid.</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - New Pricebook (Price Year)</t>
+  </si>
+  <si>
+    <t>On the New Pricebook form, type a decimal (e.g. 20.5) and a 2-digit value (e.g. 12) into Price Year, then try letters; check what is accepted and whether Save stays available.</t>
+  </si>
+  <si>
+    <t>Price Year rejects letters (the field reverts to the last valid value) but keeps a decimal (20.5) and a 2-digit value (12) without complaint. Server-side validation on final save was not exercised.</t>
+  </si>
+  <si>
+    <t>Should Price Year be restricted to a valid 4-digit year? Today only letters are blocked — 20.5 and 12 both pass the on-screen check.</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - New Pricebook (lifecycle)</t>
+  </si>
+  <si>
+    <t>Create and save a new price book, then look for any way to delete, deactivate, or remove it.</t>
+  </si>
+  <si>
+    <t>After a successful save there is no delete, deactivate, or remove option anywhere — not on the Details page, the Search action bar, any menu, or at row level. A created price book appears to be permanent via the UI.</t>
+  </si>
+  <si>
+    <t>Is there an intended way to remove or deactivate a price book created in error? This affects real-user error recovery.</t>
+  </si>
+  <si>
     <t>C1</t>
   </si>
   <si>
@@ -409,6 +478,24 @@
     <t>Testability / enablement request - submit separately from product bugs</t>
   </si>
   <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Corporate Pricing (all screens)</t>
+  </si>
+  <si>
+    <t>Inspect the Corporate Pricing screens for stable test identifiers.</t>
+  </si>
+  <si>
+    <t>The module ships with effectively no automation-grade test identifiers — Search has 3 generic ones; the Pricing Strategy, Pricing Detail, New Pricebook, Product Group Override, and Export/Import surfaces have none.</t>
+  </si>
+  <si>
+    <t>Stable, field-specific identifiers would make automated testing more reliable.</t>
+  </si>
+  <si>
+    <t>Testability / enablement request — a list of ~19 specific identifiers is provided separately. Please submit apart from the product items above.</t>
+  </si>
+  <si>
     <t>Test run summary</t>
   </si>
   <si>
@@ -425,6 +512,18 @@
   </si>
   <si>
     <t>Each item above was checked on both the current site and the previous Navigator version before being listed, so a genuine change can be told apart from long-standing behaviour.</t>
+  </si>
+  <si>
+    <t>This tracker lists 5 Corporate Pricing items raised by our testing: 1 confirmed defect (A10), 3 product/UX questions awaiting your answer (C4–C6), and 1 testability request (D2). Every item was re-checked live on the current site on 2026-06-09. A10 needs a fix; the 3 questions await a product decision; the testability request is enablement only.</t>
+  </si>
+  <si>
+    <t>Automated coverage for Corporate Pricing spans the Search page, the Pricebook Details page (both the Pricing Strategy and Pricing Detail tabs), the New Pricebook create flow, the Product Group Override screen, and the Search Export/Import toolbar. These checks run against the current site and pass.</t>
+  </si>
+  <si>
+    <t>Each item above was checked on the current site before being listed. Corporate Pricing is a new module with no equivalent on the previous Navigator version, so there is no older site to compare against; the written feature spec is used as the reference for intended behaviour, and anything we could not resolve from it is raised above as a question.</t>
+  </si>
+  <si>
+    <t>Not yet covered / paused: the full file-content round-trip for Export/Import — the on-screen triggers (the four Export/Import variants) are covered, but the exported/imported file contents depend on that feature stabilising.</t>
   </si>
 </sst>
 </file>
@@ -475,11 +574,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,44 +616,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -573,31 +681,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -625,23 +716,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -653,136 +727,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -804,18 +922,13 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -980,30 +1093,32 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="A12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="B12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F12" t="s">
+      <c r="C12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G12" t="s">
+      <c r="D12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H12" t="s">
+      <c r="E12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I12" t="s">
-        <v>34</v>
+      <c r="F12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1012,22 +1127,22 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I13" t="s">
         <v>34</v>
@@ -1039,22 +1154,22 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="I14" t="s">
         <v>34</v>
@@ -1066,19 +1181,19 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
         <v>20</v>
@@ -1093,381 +1208,577 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+      <c r="A17" s="3"/>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="I17" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" t="s">
         <v>75</v>
       </c>
-      <c r="F18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s">
         <v>20</v>
       </c>
       <c r="I19" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s">
         <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G21" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H21" t="s">
         <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F22" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H22" t="s">
         <v>20</v>
       </c>
       <c r="I22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
+      <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H23" t="s">
         <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
         <v>36</v>
       </c>
-      <c r="E24" t="s">
-        <v>106</v>
-      </c>
-      <c r="F24" t="s">
-        <v>107</v>
-      </c>
-      <c r="G24" t="s">
-        <v>108</v>
-      </c>
-      <c r="H24" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" t="s">
-        <v>46</v>
-      </c>
       <c r="E25" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F25" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G25" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H25" t="s">
         <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G26" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H26" t="s">
         <v>20</v>
       </c>
       <c r="I26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" t="s">
-        <v>109</v>
-      </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" t="s">
         <v>122</v>
       </c>
-      <c r="G27" t="s">
-        <v>113</v>
-      </c>
       <c r="H27" t="s">
         <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E28" t="s">
         <v>127</v>
       </c>
-      <c r="F28" t="s">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G28" t="s">
+      <c r="D28" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="H28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="E28" s="5" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="F28" s="5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="G28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="D29" s="5" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="E29" s="5" t="s">
         <v>135</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" t="s">
+        <v>146</v>
+      </c>
+      <c r="G31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" t="s">
+        <v>150</v>
+      </c>
+      <c r="E32" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" t="s">
+        <v>153</v>
+      </c>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>136</v>
-      </c>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
+++ b/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="178">
   <si>
     <t>COLOR KEY - our verification finding per item (rows sorted RED &gt; YELLOW &gt; GREEN within each Type section)</t>
   </si>
@@ -160,6 +160,27 @@
     <t>Action required. Confirmed live by manual entry on the current site (2026-06-09). The 100% cap itself is reasonable; the defect is the silent focus-trap with no error and no way out.</t>
   </si>
   <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Pricing Detail (New Price column)</t>
+  </si>
+  <si>
+    <t>On the Pricing Detail tab of a price book, click into a New Price cell, type an out-of-range value (e.g. 5646464), then commit it so the cell shows its error state.</t>
+  </si>
+  <si>
+    <t>As the red error icon appears, the number you typed shifts to the left to make room for the icon — the value visibly jumps sideways. The red border and icon otherwise render correctly and the value is still rejected as expected.</t>
+  </si>
+  <si>
+    <t>The error border and icon should appear without moving the entered value — the number should stay in place and the icon should sit in its own reserved space.</t>
+  </si>
+  <si>
+    <t>The error icon appears to be inserted inline within the cell and pushes the value aside, rather than occupying reserved or overlaid space.</t>
+  </si>
+  <si>
+    <t>Action required (cosmetic). Confirmed live by manual observation on the current site (2026-06-26). Validation and the disabled-Save behaviour both work and no data is lost; the issue is purely the value jumping left when the error appears. The same inline-edit control is used by other editable price cells (e.g. Max Discount, Product Group Override), so the same shift may occur there too.</t>
+  </si>
+  <si>
     <t>A1</t>
   </si>
   <si>
@@ -514,7 +535,7 @@
     <t>Each item above was checked on both the current site and the previous Navigator version before being listed, so a genuine change can be told apart from long-standing behaviour.</t>
   </si>
   <si>
-    <t>This tracker lists 5 Corporate Pricing items raised by our testing: 1 confirmed defect (A10), 3 product/UX questions awaiting your answer (C4–C6), and 1 testability request (D2). Every item was re-checked live on the current site on 2026-06-09. A10 needs a fix; the 3 questions await a product decision; the testability request is enablement only.</t>
+    <t>This tracker lists 6 Corporate Pricing items raised by our testing: 2 confirmed defects (A10–A11), 3 product/UX questions awaiting your answer (C4–C6), and 1 testability request (D2). A10 (Max Discount focus-trap) and the question/testability items were re-checked live on 2026-06-09; A11 (New Price error-icon shift) was confirmed live on 2026-06-26. A10 and A11 need fixes; the 3 questions await a product decision; the testability request is enablement only.</t>
   </si>
   <si>
     <t>Automated coverage for Corporate Pricing spans the Search page, the Pricebook Details page (both the Pricing Strategy and Pricing Detail tabs), the New Pricebook create flow, the Product Group Override screen, and the Search Export/Import toolbar. These checks run against the current site and pass.</t>
@@ -927,30 +948,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1122,30 +1143,32 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="A13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F13" t="s">
+      <c r="E13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G13" t="s">
+      <c r="F13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H13" t="s">
+      <c r="G13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I13" t="s">
-        <v>34</v>
+      <c r="H13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1154,22 +1177,22 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I14" t="s">
         <v>34</v>
@@ -1181,22 +1204,22 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="I15" t="s">
         <v>34</v>
@@ -1208,19 +1231,19 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H16" t="s">
         <v>20</v>
@@ -1235,37 +1258,37 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="I17" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="A18" s="3"/>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
         <v>78</v>
@@ -1277,282 +1300,280 @@
         <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I18" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" t="s">
         <v>82</v>
       </c>
-      <c r="D19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s">
         <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H21" t="s">
         <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H22" t="s">
         <v>20</v>
       </c>
       <c r="I22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H23" t="s">
         <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
+      <c r="A24" s="2"/>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
         <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H25" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" t="s">
         <v>36</v>
       </c>
-      <c r="E25" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" t="s">
-        <v>117</v>
-      </c>
-      <c r="H25" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" t="s">
-        <v>55</v>
-      </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H26" t="s">
         <v>20</v>
       </c>
       <c r="I26" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" t="s">
         <v>125</v>
       </c>
-      <c r="F27" t="s">
-        <v>126</v>
-      </c>
-      <c r="G27" t="s">
-        <v>122</v>
-      </c>
-      <c r="H27" t="s">
-        <v>20</v>
-      </c>
-      <c r="I27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="C28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" t="s">
+        <v>132</v>
+      </c>
+      <c r="F28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>132</v>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1560,28 +1581,28 @@
         <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1589,75 +1610,78 @@
         <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" t="s">
-        <v>143</v>
-      </c>
-      <c r="D31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F31" t="s">
+      <c r="D31" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G31" t="s">
-        <v>122</v>
-      </c>
-      <c r="H31" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="E31" s="5" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F31" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G32" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="H32" t="s">
         <v>20</v>
@@ -1667,80 +1691,93 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="B33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F33" t="s">
+        <v>159</v>
+      </c>
+      <c r="G33" t="s">
+        <v>160</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C33" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C34" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -1753,7 +1790,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -1766,7 +1803,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -1777,6 +1814,19 @@
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
     </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
+++ b/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="190">
   <si>
     <t>COLOR KEY - our verification finding per item (rows sorted RED &gt; YELLOW &gt; GREEN within each Type section)</t>
   </si>
@@ -181,6 +181,27 @@
     <t>Action required (cosmetic). Confirmed live by manual observation on the current site (2026-06-26). Validation and the disabled-Save behaviour both work and no data is lost; the issue is purely the value jumping left when the error appears. The same inline-edit control is used by other editable price cells (e.g. Max Discount, Product Group Override), so the same shift may occur there too.</t>
   </si>
   <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Product Group Override (office 1604 data &amp; import)</t>
+  </si>
+  <si>
+    <t>On the Product Group Override screen, select office 1604 in the Change Local Office picker. Then (a) click Export, and (b) try to import a price-override file for 1604 — first a file that includes the House Video Monitor product groups plus the Project Manager group, then a smaller file with only three House Video Monitor groups.</t>
+  </si>
+  <si>
+    <t>The grid shows "0 items found" for 1604, yet the Export of the same screen returns a file listing 8 override rows for 1604 — the grid and the export disagree. Importing a file that contains the Project Manager product group is rejected with a raw technical error ("An item with the same key has already been added. Key: 4543") instead of a readable message. Importing the smaller file reports "Override import complete. There were 3 override change updates.", but after reloading the grid is still empty — nothing was saved.</t>
+  </si>
+  <si>
+    <t>The grid and the Export of the same screen should agree for a location. An import should either save its rows (visible after reload) or reject them with a clear, readable message — never a raw internal error, and never a "success" message when nothing was saved.</t>
+  </si>
+  <si>
+    <t>Office 1604’s override data appears to be in an inconsistent server-side state that both hides existing rows from the grid and blocks new imports (the duplicate-key error even references a different location’s data).</t>
+  </si>
+  <si>
+    <t>Action required. Confirmed live on the current site (2026-07-06). Office 1606 works correctly on the same screen (7 rows shown, edit and save verified), so this looks specific to office 1604’s data. Our automated checks for this screen are pointed at office 1606 until this is resolved.</t>
+  </si>
+  <si>
     <t>A1</t>
   </si>
   <si>
@@ -463,6 +484,21 @@
     <t>Is there an intended way to remove or deactivate a price book created in error? This affects real-user error recovery.</t>
   </si>
   <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Product Group Override (office 1604 data)</t>
+  </si>
+  <si>
+    <t>Compare office 1604’s override data over time: earlier testing (early June) saw override rows for 1604, and a same-day Export still lists 8 rows for it, but the grid now shows none.</t>
+  </si>
+  <si>
+    <t>Office 1604’s override grid is now empty, although the Export of the same screen still returns rows for it.</t>
+  </si>
+  <si>
+    <t>Was office 1604’s override data intentionally cleaned up or reset? If so, can it be restored or repopulated so that both the grid and the import work for that location again? This determines whether our checks can return to office 1604.</t>
+  </si>
+  <si>
     <t>C1</t>
   </si>
   <si>
@@ -535,7 +571,7 @@
     <t>Each item above was checked on both the current site and the previous Navigator version before being listed, so a genuine change can be told apart from long-standing behaviour.</t>
   </si>
   <si>
-    <t>This tracker lists 6 Corporate Pricing items raised by our testing: 2 confirmed defects (A10–A11), 3 product/UX questions awaiting your answer (C4–C6), and 1 testability request (D2). A10 (Max Discount focus-trap) and the question/testability items were re-checked live on 2026-06-09; A11 (New Price error-icon shift) was confirmed live on 2026-06-26. A10 and A11 need fixes; the 3 questions await a product decision; the testability request is enablement only.</t>
+    <t>This tracker lists 8 Corporate Pricing items raised by our testing: 3 confirmed defects (A10–A12), 4 product/UX questions awaiting your answer (C4–C7), and 1 testability request (D2). A10 (Max Discount focus-trap) and the question/testability items were re-checked live on 2026-06-09; A11 (New Price error-icon shift) was confirmed live on 2026-06-26; A12 (office 1604 override data/import) and C7 (office 1604 data-restore question) were confirmed live on 2026-07-06. A10, A11 and A12 need fixes; the 4 questions await a product decision; the testability request is enablement only.</t>
   </si>
   <si>
     <t>Automated coverage for Corporate Pricing spans the Search page, the Pricebook Details page (both the Pricing Strategy and Pricing Detail tabs), the New Pricebook create flow, the Product Group Override screen, and the Search Export/Import toolbar. These checks run against the current site and pass.</t>
@@ -948,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1172,30 +1208,30 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F14" t="s">
+      <c r="E14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G14" t="s">
+      <c r="F14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H14" t="s">
+      <c r="G14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I14" t="s">
-        <v>34</v>
+      <c r="H14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1204,22 +1240,22 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I15" t="s">
         <v>34</v>
@@ -1231,22 +1267,22 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
         <v>34</v>
@@ -1258,19 +1294,19 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s">
         <v>20</v>
@@ -1285,37 +1321,37 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="I18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
+      <c r="A19" s="3"/>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
         <v>85</v>
@@ -1327,282 +1363,280 @@
         <v>87</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" t="s">
         <v>89</v>
       </c>
-      <c r="D20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" t="s">
-        <v>93</v>
-      </c>
-      <c r="H20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H21" t="s">
         <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H22" t="s">
         <v>20</v>
       </c>
       <c r="I22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H23" t="s">
         <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H24" t="s">
         <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
+      <c r="A25" s="2"/>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="E25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H25" t="s">
         <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" t="s">
         <v>36</v>
       </c>
-      <c r="E26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" t="s">
-        <v>123</v>
-      </c>
-      <c r="G26" t="s">
-        <v>124</v>
-      </c>
-      <c r="H26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" t="s">
-        <v>62</v>
-      </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G27" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H27" t="s">
         <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" t="s">
+        <v>135</v>
+      </c>
+      <c r="G28" t="s">
+        <v>136</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" t="s">
         <v>132</v>
       </c>
-      <c r="F28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G28" t="s">
-        <v>129</v>
-      </c>
-      <c r="H28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="C29" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" t="s">
+        <v>139</v>
+      </c>
+      <c r="F29" t="s">
+        <v>140</v>
+      </c>
+      <c r="G29" t="s">
         <v>136</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>139</v>
+      <c r="H29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1610,28 +1644,28 @@
         <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1639,171 +1673,201 @@
         <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="3"/>
-      <c r="B32" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="A32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F32" t="s">
+      <c r="D32" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G32" t="s">
-        <v>129</v>
-      </c>
-      <c r="H32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="E32" s="5" t="s">
         <v>154</v>
       </c>
+      <c r="F32" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" t="s">
-        <v>156</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="A33" s="6"/>
+      <c r="B33" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E33" t="s">
+      <c r="D33" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F33" t="s">
+      <c r="E33" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G33" t="s">
+      <c r="F33" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="G33" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3"/>
+      <c r="B34" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" t="s">
+        <v>163</v>
+      </c>
+      <c r="E34" t="s">
+        <v>164</v>
+      </c>
+      <c r="F34" t="s">
+        <v>165</v>
+      </c>
+      <c r="G34" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C35" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" t="s">
+        <v>170</v>
+      </c>
+      <c r="F35" t="s">
+        <v>171</v>
+      </c>
+      <c r="G35" t="s">
+        <v>172</v>
+      </c>
+      <c r="H35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I34" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>169</v>
+      <c r="C36" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -1816,7 +1880,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -1827,6 +1891,32 @@
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
     </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
+++ b/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
@@ -550,7 +550,7 @@
     <t>Stable, field-specific identifiers would make automated testing more reliable.</t>
   </si>
   <si>
-    <t>Testability / enablement request — a list of ~19 specific identifiers is provided separately. Please submit apart from the product items above.</t>
+    <t>Testability / enablement request — confirmed live on the current site (2026-07-06): the only identifiers present are a few generic component ones on Search (a card header/title and a shared checkbox that repeats across checkboxes), so they cannot target a specific control; the other Corporate Pricing screens have none, and our automated checks rely on text/role fallbacks. A list of the specific, field-level identifiers we would like added is provided separately. Please submit apart from the product items above.</t>
   </si>
   <si>
     <t>Test run summary</t>
@@ -987,27 +987,27 @@
   <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>167</v>
       </c>
@@ -1835,32 +1835,32 @@
         <v>179</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>185</v>
       </c>

--- a/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
+++ b/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="193">
   <si>
     <t>COLOR KEY - our verification finding per item (rows sorted RED &gt; YELLOW &gt; GREEN within each Type section)</t>
   </si>
@@ -133,408 +133,417 @@
     <t>Delete should remain available so the row can be removed.</t>
   </si>
   <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>Product bug</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Pricing Detail (Max Discount column)</t>
+  </si>
+  <si>
+    <t>On the Pricing Detail tab of a price book, click into a Max Discount cell, type a value over 100 (e.g. 333), then try to click or tab out of the cell.</t>
+  </si>
+  <si>
+    <t>The field will not let you leave it — clicking elsewhere or pressing Tab does nothing and the cursor stays trapped in the cell. No error message, tooltip, or validation hint is shown. The only way out is to manually lower the value to 100 or less.</t>
+  </si>
+  <si>
+    <t>An out-of-range entry should show a clear validation message AND still let the user move out of the field — it should not silently trap the cursor with no feedback.</t>
+  </si>
+  <si>
+    <t>Out-of-range input appears to block the field’s blur/commit without surfacing a validation error.</t>
+  </si>
+  <si>
+    <t>Action required. Confirmed live by manual entry on the current site (2026-06-09). The 100% cap itself is reasonable; the defect is the silent focus-trap with no error and no way out. Re-verified live 2026-07-13 (independent QA re-drive) — still reproduces exactly as described. Jira dedup not yet checked; confirm no existing NM ticket before logging.</t>
+  </si>
+  <si>
+    <t>GREEN</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Pricing Detail (New Price column)</t>
+  </si>
+  <si>
+    <t>On the Pricing Detail tab of a price book, click into a New Price cell, type an out-of-range value (e.g. 5646464), then commit it so the cell shows its error state.</t>
+  </si>
+  <si>
+    <t>As the red error icon appears, the number you typed shifts to the left to make room for the icon — the value visibly jumps sideways. The red border and icon otherwise render correctly and the value is still rejected as expected.</t>
+  </si>
+  <si>
+    <t>The error border and icon should appear without moving the entered value — the number should stay in place and the icon should sit in its own reserved space.</t>
+  </si>
+  <si>
+    <t>The error icon appears to be inserted inline within the cell and pushes the value aside, rather than occupying reserved or overlaid space.</t>
+  </si>
+  <si>
+    <t>RE-TESTED live 2026-07-13: NOT reproducible as a defect. New Price rejects the out-of-range value (aria-invalid=true, Save stays disabled) — no left-shift or bad persisted value observed on re-check. The original 2026-06-26 note may have been a misread of the same validation-block behavior visible in A10. Recommend closing without logging to Jira unless a fresh repro turns up different behavior.</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Product Group Override (office 1604 data &amp; import)</t>
+  </si>
+  <si>
+    <t>On the Product Group Override screen, select office 1604 in the Change Local Office picker. Then (a) click Export, and (b) try to import a price-override file for 1604 — first a file that includes the House Video Monitor product groups plus the Project Manager group, then a smaller file with only three House Video Monitor groups.</t>
+  </si>
+  <si>
+    <t>The grid shows "0 items found" for 1604, yet the Export of the same screen returns a file listing 8 override rows for 1604 — the grid and the export disagree. Importing a file that contains the Project Manager product group is rejected with a raw technical error ("An item with the same key has already been added. Key: 4543") instead of a readable message. Importing the smaller file reports "Override import complete. There were 3 override change updates.", but after reloading the grid is still empty — nothing was saved.</t>
+  </si>
+  <si>
+    <t>The grid and the Export of the same screen should agree for a location. An import should either save its rows (visible after reload) or reject them with a clear, readable message — never a raw internal error, and never a "success" message when nothing was saved.</t>
+  </si>
+  <si>
+    <t>Office 1604’s override data appears to be in an inconsistent server-side state that both hides existing rows from the grid and blocks new imports (the duplicate-key error even references a different location’s data).</t>
+  </si>
+  <si>
+    <t>Action required. Confirmed live on the current site (2026-07-06). Office 1606 works correctly on the same screen (7 rows shown, edit and save verified), so this looks specific to office 1604’s data. Our automated checks for this screen are pointed at office 1606 until this is resolved. Re-verified live 2026-07-13 (independent QA re-drive): 1604 API still returns HTTP 500 duplicate-key 4543; 1606 returns 200; export now shows 731 rows for 1604 (row count grew since the original 8-row observation, core defect unchanged). Jira dedup not yet checked; confirm no existing NM ticket before logging.</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>On ECT Settings, change the Benefits Multiplier, save, then reload and re-check the value.</t>
+  </si>
+  <si>
+    <t>Saving reports success, but after reload the Benefits Multiplier returns to its previous figure. Historical Subrental, changed in the same save, does remain.</t>
+  </si>
+  <si>
+    <t>The saved Benefits Multiplier value remains after reload.</t>
+  </si>
+  <si>
+    <t>The value appears to be accepted by the save but not stored.</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Local Office Settings - Basic Information</t>
+  </si>
+  <si>
+    <t>On Basic Information, toggle a room's Active state; check whether Save becomes available and whether it persists after reload.</t>
+  </si>
+  <si>
+    <t>The display changes, but Save does not become available, and after reload the room is unchanged.</t>
+  </si>
+  <si>
+    <t>Toggling Active should make Save available and the change should remain after reload.</t>
+  </si>
+  <si>
+    <t>The toggle does not appear to register the form as changed.</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Location Settings - Location Management History</t>
+  </si>
+  <si>
+    <t>On Location Management History, go to the next page, then back to page 1; check the page buttons.</t>
+  </si>
+  <si>
+    <t>After returning to page 1, the first-page and last-page buttons are no longer shown; only previous/next remain.</t>
+  </si>
+  <si>
+    <t>All four page buttons should remain available on every page.</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>Location Settings - Auto Add-On</t>
+  </si>
+  <si>
+    <t>On Auto Add-On, change a checkbox, click Home, then click Discard on the prompt; check whether the page navigates.</t>
+  </si>
+  <si>
+    <t>Clicking Discard closes the dialog but the page stays on Settings instead of going to Home.</t>
+  </si>
+  <si>
+    <t>Discard should close the dialog and continue to Home.</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>On Notes, delete a row that still contains text, save, then reload and re-check.</t>
+  </si>
+  <si>
+    <t>Saving appears to succeed, but the note is still present after reloading.</t>
+  </si>
+  <si>
+    <t>Deleting a row and saving should remove it permanently.</t>
+  </si>
+  <si>
+    <t>The deletion may not be included in what is saved.</t>
+  </si>
+  <si>
+    <t>Manual verification candidate</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Location Settings - Shared Setup Locations</t>
+  </si>
+  <si>
+    <t>On Shared Setup, add a location, save, reload; then try a row's Delete, reopen the Add dialog and search the added location and a Miami-area office, and revert a Shares Inventory change. [2026-06-02 recheck on 1604: to repro the delete bug, delete TWO rows in one page session without reloading -- the 2nd delete misbehaves.]</t>
+  </si>
+  <si>
+    <t>A row's Delete sometimes does not respond; an already-added location still appears in the dialog; searching a Miami-area office returns an empty row; reverting a Shares Inventory change leaves Save available with no net change. [2026-06-02 UPDATE on 1604: the original delete-freeze was fixed but REGRESSED into an OFF-BY-ONE -- the first delete works, but every delete after it removes the row ONE ABOVE the button clicked, and can even delete the protected self-row (1604), silently with no error. Miami-area number-search '1233' now returns the office (FIXED). Already-added-still-in-dialog still reproduces.]</t>
+  </si>
+  <si>
+    <t>Delete works after reload; already-added locations are hidden; valid offices are found; reverting to the original disables Save. Every delete (not just the first) should remove the row whose own Delete was clicked; the self-row must never be deletable.</t>
+  </si>
+  <si>
+    <t>Manual verify (bundle - confirm each behaviour separately). 2026-06-02: Miami search FIXED; delete regressed to off-by-one (new bug); already-added-in-dialog still present. Specs stay fixme.</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>Location Settings - Pricing</t>
+  </si>
+  <si>
+    <t>On Pricing, change a dropdown, a date, and the Corporate Pricing checkbox; save each, reload, and re-check.</t>
+  </si>
+  <si>
+    <t>Some saved values do not appear to remain after reload, and one save action returns a server error.</t>
+  </si>
+  <si>
+    <t>Saved pricing values should remain after reload.</t>
+  </si>
+  <si>
+    <t>Manual verify on e2e + nav2</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>On Basic Information, type an invalid phone number into Phone 1 and check for validation.</t>
+  </si>
+  <si>
+    <t>Phone 1 accepts any text, with no format validation.</t>
+  </si>
+  <si>
+    <t>Please confirm whether the absence of format validation is intended.</t>
+  </si>
+  <si>
+    <t>Manual verify + confirm intent</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>On Basic Information, check Use Equipment QC with Use Fulfillment off, then on.</t>
+  </si>
+  <si>
+    <t>Use Equipment QC appears to become available only when Use Fulfillment is enabled.</t>
+  </si>
+  <si>
+    <t>Please confirm this dependency is intended.</t>
+  </si>
+  <si>
+    <t>Manual verify (with Use Fulfillment enabled)</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>Look for a Marriott PMS Account Enabled column on the current site, then on the baseline.</t>
+  </si>
+  <si>
+    <t>A Marriott PMS Account Enabled column is referenced but is not visible on the current site.</t>
+  </si>
+  <si>
+    <t>Please confirm what this column is and when it appears.</t>
+  </si>
+  <si>
+    <t>Manual verify - check baseline first</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>Look for a Notes field in Basic Information on the current site, then on the baseline.</t>
+  </si>
+  <si>
+    <t>A Notes field in Basic Information is referenced, but no such field is visible on the current site.</t>
+  </si>
+  <si>
+    <t>Please confirm whether a Notes field exists here.</t>
+  </si>
+  <si>
+    <t>Manual verify - check baseline (appears not present)</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Navigator (location URLs)</t>
+  </si>
+  <si>
+    <t>Open an unrecognised URL under a location (for example /locations/{id}/basic-info) and observe.</t>
+  </si>
+  <si>
+    <t>The page currently loads and also shows an error message.</t>
+  </si>
+  <si>
+    <t>Please confirm the intended behaviour for unknown URLs (a clear error page, a message, or a clean redirect).</t>
+  </si>
+  <si>
+    <t>Manual verify - behaviour appears different from an earlier observation (a silent redirect); confirm current behaviour and whether other unknown URLs behave the same</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>On Notes, save and observe whether an extra empty row appears.</t>
+  </si>
+  <si>
+    <t>An empty note row appears on its own after saving.</t>
+  </si>
+  <si>
+    <t>Please confirm whether this is intended (a ready-to-use next row) or unintended.</t>
+  </si>
+  <si>
+    <t>Product / UX question</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>Clear the Return Date Offset, save, reload, and re-check.</t>
+  </si>
+  <si>
+    <t>The field now stays empty; it previously defaulted back to 1.</t>
+  </si>
+  <si>
+    <t>Question, not a defect.</t>
+  </si>
+  <si>
+    <t>Is the empty value intended, or should it reset to the default? (please confirm against baseline)</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Add a location, then reopen the Change Local Office dialog and search for it.</t>
+  </si>
+  <si>
+    <t>The already-added location still appears in the dialog.</t>
+  </si>
+  <si>
+    <t>Should already-added locations be hidden from the dialog?</t>
+  </si>
+  <si>
+    <t>YELLOW</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Pricing Detail (grid)</t>
+  </si>
+  <si>
+    <t>On the Pricing Detail tab of an existing price book, look for a way to expand a product-group row to see the items inside it.</t>
+  </si>
+  <si>
+    <t>The grid is flat — each product group is a single, non-expandable row with no way to drill into items. The written spec describes expanding a product group to show the items inside it.</t>
+  </si>
+  <si>
+    <t>Is the flat grid interim (the expandable group→items view still planned), or is the flat list the final design? Our coverage currently asserts the flat grid. Re-confirmed live 2026-07-13 — flat grid still exactly as described (2,430 rows, no expand/pagination control). Awaiting product/design decision; not yet checked against Jira.</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - New Pricebook (Price Year)</t>
+  </si>
+  <si>
+    <t>On the New Pricebook form, type a decimal (e.g. 20.5) and a 2-digit value (e.g. 12) into Price Year, then try letters; check what is accepted and whether Save stays available.</t>
+  </si>
+  <si>
+    <t>Price Year rejects letters (the field reverts to the last valid value) but keeps a decimal (20.5) and a 2-digit value (12) without complaint. Server-side validation on final save was not exercised.</t>
+  </si>
+  <si>
+    <t>Should Price Year be restricted to a valid 4-digit year? Today only letters are blocked — 20.5 and 12 both pass the on-screen check. Re-confirmed live 2026-07-13 — also exercised final Save: with Year=20.5, Save click was a silent no-op (no dialog, no network call, no validation message). Jira lead NM-2057 noted as a possible dedup candidate, not yet confirmed.</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - New Pricebook (lifecycle)</t>
+  </si>
+  <si>
+    <t>Create and save a new price book, then look for any way to delete, deactivate, or remove it.</t>
+  </si>
+  <si>
+    <t>After a successful save there is no delete, deactivate, or remove option anywhere — not on the Details page, the Search action bar, any menu, or at row level. A created price book appears to be permanent via the UI.</t>
+  </si>
+  <si>
+    <t>Is there an intended way to remove or deactivate a price book created in error? This affects real-user error recovery. Re-confirmed live 2026-07-13 via a saved throwaway pricebook (ZZZ-QA-DELETE-CHECK-0713) — no delete/deactivate/remove affordance found anywhere. Awaiting product confirmation; not yet checked against Jira.</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>Corporate Pricing - Product Group Override (office 1604 data)</t>
+  </si>
+  <si>
+    <t>Compare office 1604’s override data over time: earlier testing (early June) saw override rows for 1604, and a same-day Export still lists 8 rows for it, but the grid now shows none.</t>
+  </si>
+  <si>
+    <t>Office 1604’s override grid is now empty, although the Export of the same screen still returns rows for it.</t>
+  </si>
+  <si>
+    <t>Was office 1604’s override data intentionally cleaned up or reset? If so, can it be restored or repopulated so that both the grid and the import work for that location again? This determines whether our checks can return to office 1604. Re-confirmed live 2026-07-13 — same root cause as A12 (1604 API 500 hides existing rows; export still shows 731 rows for 1604, so no data was actually lost). Recommend tracking under A12 rather than as a separate item.</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Location Settings - Local Information + Currency (history)</t>
+  </si>
+  <si>
+    <t>Change Enable Multiday Pricing or Merchant Currency, save, then check Location Management History.</t>
+  </si>
+  <si>
+    <t>These changes are not recorded in Location Management History (and were not recorded on the previous site).</t>
+  </si>
+  <si>
+    <t>Should these changes be tracked in history? (audit-coverage / product gap)</t>
+  </si>
+  <si>
+    <t>Automation support (not a product bug)</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Shared components (pagination, sort menus, dialogs)</t>
+  </si>
+  <si>
+    <t>Inspect shared components for stable test identifiers.</t>
+  </si>
+  <si>
+    <t>Several shared components do not have stable test identifiers.</t>
+  </si>
+  <si>
+    <t>Stable identifiers would make automated testing more reliable.</t>
+  </si>
+  <si>
+    <t>Testability / enablement request - submit separately from product bugs</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Product bug</t>
-  </si>
-  <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>Corporate Pricing - Pricing Detail (Max Discount column)</t>
-  </si>
-  <si>
-    <t>On the Pricing Detail tab of a price book, click into a Max Discount cell, type a value over 100 (e.g. 333), then try to click or tab out of the cell.</t>
-  </si>
-  <si>
-    <t>The field will not let you leave it — clicking elsewhere or pressing Tab does nothing and the cursor stays trapped in the cell. No error message, tooltip, or validation hint is shown. The only way out is to manually lower the value to 100 or less.</t>
-  </si>
-  <si>
-    <t>An out-of-range entry should show a clear validation message AND still let the user move out of the field — it should not silently trap the cursor with no feedback.</t>
-  </si>
-  <si>
-    <t>Out-of-range input appears to block the field’s blur/commit without surfacing a validation error.</t>
-  </si>
-  <si>
-    <t>Action required. Confirmed live by manual entry on the current site (2026-06-09). The 100% cap itself is reasonable; the defect is the silent focus-trap with no error and no way out.</t>
-  </si>
-  <si>
-    <t>A11</t>
-  </si>
-  <si>
-    <t>Corporate Pricing - Pricing Detail (New Price column)</t>
-  </si>
-  <si>
-    <t>On the Pricing Detail tab of a price book, click into a New Price cell, type an out-of-range value (e.g. 5646464), then commit it so the cell shows its error state.</t>
-  </si>
-  <si>
-    <t>As the red error icon appears, the number you typed shifts to the left to make room for the icon — the value visibly jumps sideways. The red border and icon otherwise render correctly and the value is still rejected as expected.</t>
-  </si>
-  <si>
-    <t>The error border and icon should appear without moving the entered value — the number should stay in place and the icon should sit in its own reserved space.</t>
-  </si>
-  <si>
-    <t>The error icon appears to be inserted inline within the cell and pushes the value aside, rather than occupying reserved or overlaid space.</t>
-  </si>
-  <si>
-    <t>Action required (cosmetic). Confirmed live by manual observation on the current site (2026-06-26). Validation and the disabled-Save behaviour both work and no data is lost; the issue is purely the value jumping left when the error appears. The same inline-edit control is used by other editable price cells (e.g. Max Discount, Product Group Override), so the same shift may occur there too.</t>
-  </si>
-  <si>
-    <t>A12</t>
-  </si>
-  <si>
-    <t>Corporate Pricing - Product Group Override (office 1604 data &amp; import)</t>
-  </si>
-  <si>
-    <t>On the Product Group Override screen, select office 1604 in the Change Local Office picker. Then (a) click Export, and (b) try to import a price-override file for 1604 — first a file that includes the House Video Monitor product groups plus the Project Manager group, then a smaller file with only three House Video Monitor groups.</t>
-  </si>
-  <si>
-    <t>The grid shows "0 items found" for 1604, yet the Export of the same screen returns a file listing 8 override rows for 1604 — the grid and the export disagree. Importing a file that contains the Project Manager product group is rejected with a raw technical error ("An item with the same key has already been added. Key: 4543") instead of a readable message. Importing the smaller file reports "Override import complete. There were 3 override change updates.", but after reloading the grid is still empty — nothing was saved.</t>
-  </si>
-  <si>
-    <t>The grid and the Export of the same screen should agree for a location. An import should either save its rows (visible after reload) or reject them with a clear, readable message — never a raw internal error, and never a "success" message when nothing was saved.</t>
-  </si>
-  <si>
-    <t>Office 1604’s override data appears to be in an inconsistent server-side state that both hides existing rows from the grid and blocks new imports (the duplicate-key error even references a different location’s data).</t>
-  </si>
-  <si>
-    <t>Action required. Confirmed live on the current site (2026-07-06). Office 1606 works correctly on the same screen (7 rows shown, edit and save verified), so this looks specific to office 1604’s data. Our automated checks for this screen are pointed at office 1606 until this is resolved.</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>On ECT Settings, change the Benefits Multiplier, save, then reload and re-check the value.</t>
-  </si>
-  <si>
-    <t>Saving reports success, but after reload the Benefits Multiplier returns to its previous figure. Historical Subrental, changed in the same save, does remain.</t>
-  </si>
-  <si>
-    <t>The saved Benefits Multiplier value remains after reload.</t>
-  </si>
-  <si>
-    <t>The value appears to be accepted by the save but not stored.</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>Local Office Settings - Basic Information</t>
-  </si>
-  <si>
-    <t>On Basic Information, toggle a room's Active state; check whether Save becomes available and whether it persists after reload.</t>
-  </si>
-  <si>
-    <t>The display changes, but Save does not become available, and after reload the room is unchanged.</t>
-  </si>
-  <si>
-    <t>Toggling Active should make Save available and the change should remain after reload.</t>
-  </si>
-  <si>
-    <t>The toggle does not appear to register the form as changed.</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>Location Settings - Location Management History</t>
-  </si>
-  <si>
-    <t>On Location Management History, go to the next page, then back to page 1; check the page buttons.</t>
-  </si>
-  <si>
-    <t>After returning to page 1, the first-page and last-page buttons are no longer shown; only previous/next remain.</t>
-  </si>
-  <si>
-    <t>All four page buttons should remain available on every page.</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>Location Settings - Auto Add-On</t>
-  </si>
-  <si>
-    <t>On Auto Add-On, change a checkbox, click Home, then click Discard on the prompt; check whether the page navigates.</t>
-  </si>
-  <si>
-    <t>Clicking Discard closes the dialog but the page stays on Settings instead of going to Home.</t>
-  </si>
-  <si>
-    <t>Discard should close the dialog and continue to Home.</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <t>On Notes, delete a row that still contains text, save, then reload and re-check.</t>
-  </si>
-  <si>
-    <t>Saving appears to succeed, but the note is still present after reloading.</t>
-  </si>
-  <si>
-    <t>Deleting a row and saving should remove it permanently.</t>
-  </si>
-  <si>
-    <t>The deletion may not be included in what is saved.</t>
-  </si>
-  <si>
-    <t>Manual verification candidate</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>Location Settings - Shared Setup Locations</t>
-  </si>
-  <si>
-    <t>On Shared Setup, add a location, save, reload; then try a row's Delete, reopen the Add dialog and search the added location and a Miami-area office, and revert a Shares Inventory change. [2026-06-02 recheck on 1604: to repro the delete bug, delete TWO rows in one page session without reloading -- the 2nd delete misbehaves.]</t>
-  </si>
-  <si>
-    <t>A row's Delete sometimes does not respond; an already-added location still appears in the dialog; searching a Miami-area office returns an empty row; reverting a Shares Inventory change leaves Save available with no net change. [2026-06-02 UPDATE on 1604: the original delete-freeze was fixed but REGRESSED into an OFF-BY-ONE -- the first delete works, but every delete after it removes the row ONE ABOVE the button clicked, and can even delete the protected self-row (1604), silently with no error. Miami-area number-search '1233' now returns the office (FIXED). Already-added-still-in-dialog still reproduces.]</t>
-  </si>
-  <si>
-    <t>Delete works after reload; already-added locations are hidden; valid offices are found; reverting to the original disables Save. Every delete (not just the first) should remove the row whose own Delete was clicked; the self-row must never be deletable.</t>
-  </si>
-  <si>
-    <t>Manual verify (bundle - confirm each behaviour separately). 2026-06-02: Miami search FIXED; delete regressed to off-by-one (new bug); already-added-in-dialog still present. Specs stay fixme.</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>Location Settings - Pricing</t>
-  </si>
-  <si>
-    <t>On Pricing, change a dropdown, a date, and the Corporate Pricing checkbox; save each, reload, and re-check.</t>
-  </si>
-  <si>
-    <t>Some saved values do not appear to remain after reload, and one save action returns a server error.</t>
-  </si>
-  <si>
-    <t>Saved pricing values should remain after reload.</t>
-  </si>
-  <si>
-    <t>Manual verify on e2e + nav2</t>
-  </si>
-  <si>
-    <t>B5</t>
-  </si>
-  <si>
-    <t>On Basic Information, type an invalid phone number into Phone 1 and check for validation.</t>
-  </si>
-  <si>
-    <t>Phone 1 accepts any text, with no format validation.</t>
-  </si>
-  <si>
-    <t>Please confirm whether the absence of format validation is intended.</t>
-  </si>
-  <si>
-    <t>Manual verify + confirm intent</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
-    <t>On Basic Information, check Use Equipment QC with Use Fulfillment off, then on.</t>
-  </si>
-  <si>
-    <t>Use Equipment QC appears to become available only when Use Fulfillment is enabled.</t>
-  </si>
-  <si>
-    <t>Please confirm this dependency is intended.</t>
-  </si>
-  <si>
-    <t>Manual verify (with Use Fulfillment enabled)</t>
-  </si>
-  <si>
-    <t>B7</t>
-  </si>
-  <si>
-    <t>Look for a Marriott PMS Account Enabled column on the current site, then on the baseline.</t>
-  </si>
-  <si>
-    <t>A Marriott PMS Account Enabled column is referenced but is not visible on the current site.</t>
-  </si>
-  <si>
-    <t>Please confirm what this column is and when it appears.</t>
-  </si>
-  <si>
-    <t>Manual verify - check baseline first</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
-    <t>Look for a Notes field in Basic Information on the current site, then on the baseline.</t>
-  </si>
-  <si>
-    <t>A Notes field in Basic Information is referenced, but no such field is visible on the current site.</t>
-  </si>
-  <si>
-    <t>Please confirm whether a Notes field exists here.</t>
-  </si>
-  <si>
-    <t>Manual verify - check baseline (appears not present)</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>Navigator (location URLs)</t>
-  </si>
-  <si>
-    <t>Open an unrecognised URL under a location (for example /locations/{id}/basic-info) and observe.</t>
-  </si>
-  <si>
-    <t>The page currently loads and also shows an error message.</t>
-  </si>
-  <si>
-    <t>Please confirm the intended behaviour for unknown URLs (a clear error page, a message, or a clean redirect).</t>
-  </si>
-  <si>
-    <t>Manual verify - behaviour appears different from an earlier observation (a silent redirect); confirm current behaviour and whether other unknown URLs behave the same</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>On Notes, save and observe whether an extra empty row appears.</t>
-  </si>
-  <si>
-    <t>An empty note row appears on its own after saving.</t>
-  </si>
-  <si>
-    <t>Please confirm whether this is intended (a ready-to-use next row) or unintended.</t>
-  </si>
-  <si>
-    <t>Product / UX question</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>Clear the Return Date Offset, save, reload, and re-check.</t>
-  </si>
-  <si>
-    <t>The field now stays empty; it previously defaulted back to 1.</t>
-  </si>
-  <si>
-    <t>Question, not a defect.</t>
-  </si>
-  <si>
-    <t>Is the empty value intended, or should it reset to the default? (please confirm against baseline)</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Add a location, then reopen the Change Local Office dialog and search for it.</t>
-  </si>
-  <si>
-    <t>The already-added location still appears in the dialog.</t>
-  </si>
-  <si>
-    <t>Should already-added locations be hidden from the dialog?</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>Corporate Pricing - Pricing Detail (grid)</t>
-  </si>
-  <si>
-    <t>On the Pricing Detail tab of an existing price book, look for a way to expand a product-group row to see the items inside it.</t>
-  </si>
-  <si>
-    <t>The grid is flat — each product group is a single, non-expandable row with no way to drill into items. The written spec describes expanding a product group to show the items inside it.</t>
-  </si>
-  <si>
-    <t>Is the flat grid interim (the expandable group→items view still planned), or is the flat list the final design? Our coverage currently asserts the flat grid.</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>Corporate Pricing - New Pricebook (Price Year)</t>
-  </si>
-  <si>
-    <t>On the New Pricebook form, type a decimal (e.g. 20.5) and a 2-digit value (e.g. 12) into Price Year, then try letters; check what is accepted and whether Save stays available.</t>
-  </si>
-  <si>
-    <t>Price Year rejects letters (the field reverts to the last valid value) but keeps a decimal (20.5) and a 2-digit value (12) without complaint. Server-side validation on final save was not exercised.</t>
-  </si>
-  <si>
-    <t>Should Price Year be restricted to a valid 4-digit year? Today only letters are blocked — 20.5 and 12 both pass the on-screen check.</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>Corporate Pricing - New Pricebook (lifecycle)</t>
-  </si>
-  <si>
-    <t>Create and save a new price book, then look for any way to delete, deactivate, or remove it.</t>
-  </si>
-  <si>
-    <t>After a successful save there is no delete, deactivate, or remove option anywhere — not on the Details page, the Search action bar, any menu, or at row level. A created price book appears to be permanent via the UI.</t>
-  </si>
-  <si>
-    <t>Is there an intended way to remove or deactivate a price book created in error? This affects real-user error recovery.</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>Corporate Pricing - Product Group Override (office 1604 data)</t>
-  </si>
-  <si>
-    <t>Compare office 1604’s override data over time: earlier testing (early June) saw override rows for 1604, and a same-day Export still lists 8 rows for it, but the grid now shows none.</t>
-  </si>
-  <si>
-    <t>Office 1604’s override grid is now empty, although the Export of the same screen still returns rows for it.</t>
-  </si>
-  <si>
-    <t>Was office 1604’s override data intentionally cleaned up or reset? If so, can it be restored or repopulated so that both the grid and the import work for that location again? This determines whether our checks can return to office 1604.</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>Location Settings - Local Information + Currency (history)</t>
-  </si>
-  <si>
-    <t>Change Enable Multiday Pricing or Merchant Currency, save, then check Location Management History.</t>
-  </si>
-  <si>
-    <t>These changes are not recorded in Location Management History (and were not recorded on the previous site).</t>
-  </si>
-  <si>
-    <t>Should these changes be tracked in history? (audit-coverage / product gap)</t>
-  </si>
-  <si>
-    <t>Automation support (not a product bug)</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>Shared components (pagination, sort menus, dialogs)</t>
-  </si>
-  <si>
-    <t>Inspect shared components for stable test identifiers.</t>
-  </si>
-  <si>
-    <t>Several shared components do not have stable test identifiers.</t>
-  </si>
-  <si>
-    <t>Stable identifiers would make automated testing more reliable.</t>
-  </si>
-  <si>
-    <t>Testability / enablement request - submit separately from product bugs</t>
-  </si>
-  <si>
     <t>D2</t>
   </si>
   <si>
@@ -550,7 +559,7 @@
     <t>Stable, field-specific identifiers would make automated testing more reliable.</t>
   </si>
   <si>
-    <t>Testability / enablement request — confirmed live on the current site (2026-07-06): the only identifiers present are a few generic component ones on Search (a card header/title and a shared checkbox that repeats across checkboxes), so they cannot target a specific control; the other Corporate Pricing screens have none, and our automated checks rely on text/role fallbacks. A list of the specific, field-level identifiers we would like added is provided separately. Please submit apart from the product items above.</t>
+    <t>Testability / enablement request — confirmed live on the current site (2026-07-06): the only identifiers present are a few generic component ones on Search (a card header/title and a shared checkbox that repeats across checkboxes), so they cannot target a specific control; the other Corporate Pricing screens have none, and our automated checks rely on text/role fallbacks. A list of the specific, field-level identifiers we would like added is provided separately. Please submit apart from the product items above. Re-confirmed live 2026-07-13 — Search remains the only screen with any testid coverage (3 unique generic values); the other 5 screens/tabs have none.</t>
   </si>
   <si>
     <t>Test run summary</t>
@@ -986,6 +995,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1180,58 +1199,60 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="B14" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1240,22 +1261,22 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I15" t="s">
         <v>34</v>
@@ -1267,22 +1288,22 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s">
         <v>34</v>
@@ -1294,19 +1315,19 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
         <v>20</v>
@@ -1321,19 +1342,19 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s">
         <v>20</v>
@@ -1348,22 +1369,22 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s">
         <v>34</v>
@@ -1372,502 +1393,504 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s">
         <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H21" t="s">
         <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H22" t="s">
         <v>20</v>
       </c>
       <c r="I22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H23" t="s">
         <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H24" t="s">
         <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H25" t="s">
         <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H26" t="s">
         <v>20</v>
       </c>
       <c r="I26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
         <v>36</v>
       </c>
       <c r="E27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H27" t="s">
         <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H28" t="s">
         <v>20</v>
       </c>
       <c r="I28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H29" t="s">
         <v>20</v>
       </c>
       <c r="I29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
+      <c r="A33" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="B33" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E34" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H34" t="s">
         <v>20</v>
       </c>
       <c r="I34" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D35" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E35" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H35" t="s">
         <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -1880,7 +1903,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -1893,7 +1916,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -1906,7 +1929,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>

--- a/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
+++ b/clients/encore/test_cases_xlsx/encore-qa-tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="192">
   <si>
     <t>COLOR KEY - our verification finding per item (rows sorted RED &gt; YELLOW &gt; GREEN within each Type section)</t>
   </si>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>Action required. Confirmed live by manual entry on the current site (2026-06-09). The 100% cap itself is reasonable; the defect is the silent focus-trap with no error and no way out. Re-verified live 2026-07-13 (independent QA re-drive) — still reproduces exactly as described. Jira dedup not yet checked; confirm no existing NM ticket before logging.</t>
-  </si>
-  <si>
-    <t>GREEN</t>
   </si>
   <si>
     <t>A11</t>
@@ -1199,31 +1196,31 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1234,25 +1231,25 @@
         <v>41</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1261,22 +1258,22 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
         <v>65</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>66</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>67</v>
-      </c>
-      <c r="H15" t="s">
-        <v>68</v>
       </c>
       <c r="I15" t="s">
         <v>34</v>
@@ -1288,22 +1285,22 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
         <v>69</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>70</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>71</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>72</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>73</v>
-      </c>
-      <c r="H16" t="s">
-        <v>74</v>
       </c>
       <c r="I16" t="s">
         <v>34</v>
@@ -1315,19 +1312,19 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
         <v>75</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>76</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>77</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>78</v>
-      </c>
-      <c r="G17" t="s">
-        <v>79</v>
       </c>
       <c r="H17" t="s">
         <v>20</v>
@@ -1342,19 +1339,19 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
         <v>80</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>81</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>82</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>83</v>
-      </c>
-      <c r="G18" t="s">
-        <v>84</v>
       </c>
       <c r="H18" t="s">
         <v>20</v>
@@ -1369,22 +1366,22 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" t="s">
         <v>86</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>87</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>88</v>
-      </c>
-      <c r="H19" t="s">
-        <v>89</v>
       </c>
       <c r="I19" t="s">
         <v>34</v>
@@ -1393,504 +1390,504 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
         <v>90</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>91</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>92</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>93</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>94</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
         <v>95</v>
-      </c>
-      <c r="H20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
         <v>97</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>98</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>99</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>100</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" t="s">
         <v>101</v>
-      </c>
-      <c r="H21" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" t="s">
         <v>103</v>
       </c>
-      <c r="D22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>104</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>105</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
         <v>106</v>
-      </c>
-      <c r="H22" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" t="s">
         <v>108</v>
       </c>
-      <c r="D23" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>109</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>110</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" t="s">
         <v>111</v>
-      </c>
-      <c r="H23" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" t="s">
         <v>113</v>
       </c>
-      <c r="D24" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>114</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>115</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s">
         <v>116</v>
-      </c>
-      <c r="H24" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" t="s">
         <v>118</v>
       </c>
-      <c r="D25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>119</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>120</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" t="s">
         <v>121</v>
-      </c>
-      <c r="H25" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
         <v>123</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>124</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>125</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>126</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" t="s">
         <v>127</v>
-      </c>
-      <c r="H26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>36</v>
       </c>
       <c r="E27" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" t="s">
         <v>130</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>131</v>
       </c>
-      <c r="G27" t="s">
-        <v>132</v>
-      </c>
       <c r="H27" t="s">
         <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
         <v>133</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" t="s">
         <v>134</v>
       </c>
-      <c r="D28" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>135</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>136</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
         <v>137</v>
-      </c>
-      <c r="H28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" t="s">
         <v>139</v>
       </c>
-      <c r="D29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>140</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" t="s">
         <v>141</v>
-      </c>
-      <c r="G29" t="s">
-        <v>137</v>
-      </c>
-      <c r="H29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I29" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" t="s">
         <v>164</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>165</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>166</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
         <v>167</v>
-      </c>
-      <c r="G34" t="s">
-        <v>137</v>
-      </c>
-      <c r="H34" t="s">
-        <v>20</v>
-      </c>
-      <c r="I34" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" t="s">
         <v>169</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>170</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>171</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>172</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>173</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
         <v>174</v>
-      </c>
-      <c r="H35" t="s">
-        <v>20</v>
-      </c>
-      <c r="I35" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="H36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -1903,7 +1900,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -1916,7 +1913,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -1929,7 +1926,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
